--- a/小程序配置表.xlsx
+++ b/小程序配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>场景名</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>到首页 tab 页即可</t>
+  </si>
+  <si>
+    <t>明日开课通知</t>
+  </si>
+  <si>
+    <t>aVKlwM2zva8WuT04AdaibI6akNh8aoPjn3oKzWE-SLA</t>
+  </si>
+  <si>
+    <t>开始时间（每天早上 6 点）、活动名称（期次名称+“晨读营”）、活动内容（当天学习课程名称）、参与方式（进入凡人共读小程序）</t>
   </si>
 </sst>
 </file>
@@ -1270,8 +1279,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.1538461538462" customWidth="1"/>
     <col min="2" max="2" width="55.3846153846154" customWidth="1"/>
@@ -1382,6 +1391,23 @@
         <v>25</v>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
